--- a/docs/test-samples/00-시험표.xlsx
+++ b/docs/test-samples/00-시험표.xlsx
@@ -70,10 +70,10 @@
     <t>3-돈육상사-두칸서식.xlsx</t>
   </si>
   <si>
-    <t>엑셀 파일과 쉼표 숫자, 묶음+개체 두 칸 서식. 첫 칸 '번호'(일련번호)가 등급으로 잘못 잡히는 사례</t>
-  </si>
-  <si>
-    <t>묶음번호와 이력번호가 따로 잡히고 단가 13,000이 숫자로 읽힘. 첫 칸이 '등급'으로 잡혀 있으면 그 칸 선택을 '없음'으로 고치고 저장(→ 같은 공급처를 다시 올릴 때 기억되는지 확인)</t>
+    <t>엑셀 파일과 쉼표 숫자, 묶음+개체 두 칸 서식. 첫 칸 '번호'(일련번호 1·2·3)는 등급으로 잡히지 않아야 함</t>
+  </si>
+  <si>
+    <t>묶음번호와 이력번호가 따로 잡히고 단가 13,000이 숫자로 읽힘. 부위는 품목명(삼겹살·목살)에서 채워짐. 등급 칸은 '없음'. 저장 후 같은 공급처를 다시 올릴 때 칸 배치가 기억되는지 확인</t>
   </si>
   <si>
     <t>100770123456 을 12.5kg, 100770123457 을 12.3kg</t>
